--- a/artfynd/A 8219-2025 artfynd.xlsx
+++ b/artfynd/A 8219-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ84"/>
+  <dimension ref="A1:AZ88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -996,45 +996,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126355571</v>
+        <v>137515730</v>
       </c>
       <c r="B5" t="n">
-        <v>97358</v>
+        <v>99352</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>219790</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Järnforsen, Järnforsen, Ly lm</t>
+          <t>Arjeplog - Storuman, Ly lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>559812</v>
+        <v>559857</v>
       </c>
       <c r="R5" t="n">
-        <v>7309847</v>
+        <v>7310124</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,12 +1061,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>hundratals</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1077,71 +1082,74 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Bördig grannaturskog vid bäckravin</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Nathalie Edwards</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>C260071 AVK Arjeplog - Storuman</t>
+        </is>
+      </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126355571</t>
+          <t>https://artportalen.se/Sighting/137515730</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126356440</v>
+        <v>137515731</v>
       </c>
       <c r="B6" t="n">
-        <v>92208</v>
+        <v>99352</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>219790</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Järnforsen, Järnforsen, Ly lm</t>
+          <t>Arjeplog - Storuman, Ly lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>559675</v>
+        <v>559947</v>
       </c>
       <c r="R6" t="n">
-        <v>7310094</v>
+        <v>7309926</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,12 +1176,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1184,71 +1192,74 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Bördig grannaturskog i brant terräng</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>C260071 AVK Arjeplog - Storuman</t>
+        </is>
+      </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126356440</t>
+          <t>https://artportalen.se/Sighting/137515731</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126356501</v>
+        <v>137515732</v>
       </c>
       <c r="B7" t="n">
-        <v>91905</v>
+        <v>99352</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>219790</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Järnforsen, Järnforsen, Ly lm</t>
+          <t>Arjeplog - Storuman, Ly lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>559697</v>
+        <v>559912</v>
       </c>
       <c r="R7" t="n">
-        <v>7310125</v>
+        <v>7309992</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1275,12 +1286,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ett hundratal</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1291,36 +1307,35 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Bördig grannaturskog i brant terräng</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Nathalie Edwards</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>C260071 AVK Arjeplog - Storuman</t>
+        </is>
+      </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126356501</t>
+          <t>https://artportalen.se/Sighting/137515732</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126356436</v>
+        <v>126355571</v>
       </c>
       <c r="B8" t="n">
-        <v>91909</v>
+        <v>97358</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,21 +1343,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1367,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>559675</v>
+        <v>559812</v>
       </c>
       <c r="R8" t="n">
-        <v>7310094</v>
+        <v>7309847</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1401,7 +1416,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Bördig grannaturskog i brant terräng</t>
+          <t>Bördig grannaturskog vid bäckravin</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1418,54 +1433,51 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126356436</t>
+          <t>https://artportalen.se/Sighting/126355571</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126355857</v>
+        <v>126356440</v>
       </c>
       <c r="B9" t="n">
-        <v>91923</v>
+        <v>92208</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Järnforsen, Järnforsen, Ly lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>559755</v>
+        <v>559675</v>
       </c>
       <c r="R9" t="n">
-        <v>7309933</v>
+        <v>7310094</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1506,13 +1518,12 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Yngre, tidigare avverkad/gallrad skog med många lämnade lågor och naturvärdesträd.</t>
+          <t>Bördig grannaturskog i brant terräng</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1529,38 +1540,38 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126355857</t>
+          <t>https://artportalen.se/Sighting/126356440</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126356490</v>
+        <v>126356501</v>
       </c>
       <c r="B10" t="n">
-        <v>91923</v>
+        <v>91905</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1204</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1570,7 +1581,7 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>559674</v>
+        <v>559697</v>
       </c>
       <c r="R10" t="n">
         <v>7310125</v>
@@ -1636,38 +1647,38 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126356490</t>
+          <t>https://artportalen.se/Sighting/126356501</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126356815</v>
+        <v>126356436</v>
       </c>
       <c r="B11" t="n">
-        <v>91923</v>
+        <v>91909</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1677,10 +1688,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>559785</v>
+        <v>559675</v>
       </c>
       <c r="R11" t="n">
-        <v>7310073</v>
+        <v>7310094</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1743,13 +1754,13 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126356815</t>
+          <t>https://artportalen.se/Sighting/126356436</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126357095</v>
+        <v>126355857</v>
       </c>
       <c r="B12" t="n">
         <v>91923</v>
@@ -1778,16 +1789,19 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Järnforsen, Järnforsen, Ly lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>559794</v>
+        <v>559755</v>
       </c>
       <c r="R12" t="n">
-        <v>7309792</v>
+        <v>7309933</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1828,12 +1842,13 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Bördig grannaturskog i brant terräng</t>
+          <t>Yngre, tidigare avverkad/gallrad skog med många lämnade lågor och naturvärdesträd.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1850,16 +1865,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126357095</t>
+          <t>https://artportalen.se/Sighting/126355857</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126355561</v>
+        <v>126356490</v>
       </c>
       <c r="B13" t="n">
-        <v>92283</v>
+        <v>91923</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1867,21 +1882,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2063</v>
+        <v>1204</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1891,10 +1906,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>559811</v>
+        <v>559674</v>
       </c>
       <c r="R13" t="n">
-        <v>7309839</v>
+        <v>7310125</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1940,7 +1955,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Bördig grannaturskog vid bäckravin</t>
+          <t>Bördig grannaturskog i brant terräng</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -1957,54 +1972,51 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126355561</t>
+          <t>https://artportalen.se/Sighting/126356490</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127275517</v>
+        <v>126356815</v>
       </c>
       <c r="B14" t="n">
-        <v>80433</v>
+        <v>91923</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>1204</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Järnforsen, Järnforsen, Ly lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>559782</v>
+        <v>559785</v>
       </c>
       <c r="R14" t="n">
-        <v>7310143</v>
+        <v>7310073</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2031,12 +2043,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2045,56 +2057,60 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Bördig grannaturskog i brant terräng</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Olle Amcoff</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Olle Amcoff</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127275517</t>
+          <t>https://artportalen.se/Sighting/126356815</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126356649</v>
+        <v>126357095</v>
       </c>
       <c r="B15" t="n">
-        <v>92869</v>
+        <v>91923</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4769</v>
+        <v>1204</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2104,10 +2120,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>559746</v>
+        <v>559794</v>
       </c>
       <c r="R15" t="n">
-        <v>7310123</v>
+        <v>7309792</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2170,38 +2186,38 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126356649</t>
+          <t>https://artportalen.se/Sighting/126357095</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127274996</v>
+        <v>126355561</v>
       </c>
       <c r="B16" t="n">
-        <v>79413</v>
+        <v>92283</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6450</v>
+        <v>2063</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2211,10 +2227,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>559768</v>
+        <v>559811</v>
       </c>
       <c r="R16" t="n">
-        <v>7310262</v>
+        <v>7309839</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2241,12 +2257,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2257,69 +2273,77 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Bördig grannaturskog vid bäckravin</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Olle Amcoff</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Olle Amcoff</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127274996</t>
+          <t>https://artportalen.se/Sighting/126355561</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127274895</v>
+        <v>127275517</v>
       </c>
       <c r="B17" t="n">
-        <v>80467</v>
+        <v>80433</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Järnforsen, Järnforsen, Ly lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>559774</v>
+        <v>559782</v>
       </c>
       <c r="R17" t="n">
-        <v>7310261</v>
+        <v>7310143</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2357,6 +2381,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2374,16 +2399,16 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127274895</t>
+          <t>https://artportalen.se/Sighting/127275517</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126356631</v>
+        <v>126356649</v>
       </c>
       <c r="B18" t="n">
-        <v>99022</v>
+        <v>92869</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2391,21 +2416,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220093</v>
+        <v>4769</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2418,7 +2443,7 @@
         <v>559746</v>
       </c>
       <c r="R18" t="n">
-        <v>7310122</v>
+        <v>7310123</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2481,16 +2506,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126356631</t>
+          <t>https://artportalen.se/Sighting/126356649</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126357389</v>
+        <v>127274996</v>
       </c>
       <c r="B19" t="n">
-        <v>91905</v>
+        <v>79413</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2498,37 +2523,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>6450</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Järnforsen, Järnforsen, Ly lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>560081</v>
+        <v>559768</v>
       </c>
       <c r="R19" t="n">
-        <v>7309611</v>
+        <v>7310262</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2555,12 +2577,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2569,61 +2591,55 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>Bördig grannaturskog i brant terräng</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Olle Amcoff</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Olle Amcoff</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126357389</t>
+          <t>https://artportalen.se/Sighting/127274996</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126359227</v>
+        <v>127274895</v>
       </c>
       <c r="B20" t="n">
-        <v>83307</v>
+        <v>80467</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>6463</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2633,13 +2649,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>560045</v>
+        <v>559774</v>
       </c>
       <c r="R20" t="n">
-        <v>7309792</v>
+        <v>7310261</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2663,12 +2679,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2679,74 +2695,66 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>Gransumpskog</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Olle Amcoff</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Olle Amcoff</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126359227</t>
+          <t>https://artportalen.se/Sighting/127274895</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126358063</v>
+        <v>126356631</v>
       </c>
       <c r="B21" t="n">
-        <v>83299</v>
+        <v>99022</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>308</v>
+        <v>220093</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Jipmomyran, Jipmomyran, Ly lm</t>
+          <t>Järnforsen, Järnforsen, Ly lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>560358</v>
+        <v>559746</v>
       </c>
       <c r="R21" t="n">
-        <v>7309396</v>
+        <v>7310122</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2787,13 +2795,12 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Frodig, urskogsartad granskog i brant terräng</t>
+          <t>Bördig grannaturskog i brant terräng</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2810,38 +2817,38 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126358063</t>
+          <t>https://artportalen.se/Sighting/126356631</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126358035</v>
+        <v>126357389</v>
       </c>
       <c r="B22" t="n">
-        <v>83298</v>
+        <v>91905</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>492</v>
+        <v>1108</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2850,14 +2857,14 @@
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Jipmomyran, Jipmomyran, Ly lm</t>
+          <t>Järnforsen, Järnforsen, Ly lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>560363</v>
+        <v>560081</v>
       </c>
       <c r="R22" t="n">
-        <v>7309388</v>
+        <v>7309611</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2904,7 +2911,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Frodig, urskogsartad granskog i brant terräng</t>
+          <t>Bördig grannaturskog i brant terräng</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -2921,54 +2928,51 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126358035</t>
+          <t>https://artportalen.se/Sighting/126357389</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126357490</v>
+        <v>126359227</v>
       </c>
       <c r="B23" t="n">
-        <v>92721</v>
+        <v>83307</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>918</v>
+        <v>6440</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Järnforsen, Järnforsen, Ly lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>560120</v>
+        <v>560045</v>
       </c>
       <c r="R23" t="n">
-        <v>7309549</v>
+        <v>7309792</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3009,13 +3013,12 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Frodig, urskogsartad granskog i brant terräng</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3032,54 +3035,55 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126357490</t>
+          <t>https://artportalen.se/Sighting/126359227</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126357916</v>
+        <v>137515733</v>
       </c>
       <c r="B24" t="n">
-        <v>92721</v>
+        <v>99352</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>918</v>
+        <v>219790</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Jipmomyran, Jipmomyran, Ly lm</t>
+          <t>Arjeplog - Storuman, Ly lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>560301</v>
+        <v>560040</v>
       </c>
       <c r="R24" t="n">
-        <v>7309435</v>
+        <v>7309784</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3106,12 +3110,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>50 talet spridda genom objektet</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3120,39 +3129,37 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>Frodig, urskogsartad granskog i brant terräng</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>C260071 AVK Arjeplog - Storuman</t>
+        </is>
+      </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126357916</t>
+          <t>https://artportalen.se/Sighting/137515733</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>66544349</v>
+        <v>126358063</v>
       </c>
       <c r="B25" t="n">
-        <v>91905</v>
+        <v>83299</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3160,37 +3167,40 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1108</v>
+        <v>308</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Djupfors V, Ly lm</t>
+          <t>Jipmomyran, Jipmomyran, Ly lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>560829</v>
+        <v>560358</v>
       </c>
       <c r="R25" t="n">
-        <v>7309022</v>
+        <v>7309396</v>
       </c>
       <c r="S25" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3214,12 +3224,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2014-09-05</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2014-09-05</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3228,60 +3238,61 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
-      <c r="AR25" t="inlineStr">
-        <is>
-          <t>25090</t>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Frodig, urskogsartad granskog i brant terräng</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Malin Sahlin</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66544349</t>
+          <t>https://artportalen.se/Sighting/126358063</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126357718</v>
+        <v>126358035</v>
       </c>
       <c r="B26" t="n">
-        <v>91905</v>
+        <v>83298</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1108</v>
+        <v>492</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3294,10 +3305,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>560264</v>
+        <v>560363</v>
       </c>
       <c r="R26" t="n">
-        <v>7309462</v>
+        <v>7309388</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3361,51 +3372,54 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126357718</t>
+          <t>https://artportalen.se/Sighting/126358035</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126359216</v>
+        <v>126357490</v>
       </c>
       <c r="B27" t="n">
-        <v>91905</v>
+        <v>92721</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1108</v>
+        <v>918</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Jipmomyran, Jipmomyran, Ly lm</t>
+          <t>Järnforsen, Järnforsen, Ly lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>560542</v>
+        <v>560120</v>
       </c>
       <c r="R27" t="n">
-        <v>7309328</v>
+        <v>7309549</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3446,12 +3460,13 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Lövrik grannaturskog</t>
+          <t>Frodig, urskogsartad granskog i brant terräng</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3468,38 +3483,38 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126359216</t>
+          <t>https://artportalen.se/Sighting/126357490</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126358040</v>
+        <v>126357916</v>
       </c>
       <c r="B28" t="n">
-        <v>83312</v>
+        <v>92721</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1467</v>
+        <v>918</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3512,10 +3527,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>560363</v>
+        <v>560301</v>
       </c>
       <c r="R28" t="n">
-        <v>7309388</v>
+        <v>7309435</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3579,16 +3594,16 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126358040</t>
+          <t>https://artportalen.se/Sighting/126357916</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126357748</v>
+        <v>66544349</v>
       </c>
       <c r="B29" t="n">
-        <v>80433</v>
+        <v>91905</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3596,40 +3611,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Jipmomyran, Jipmomyran, Ly lm</t>
+          <t>Djupfors V, Ly lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>560277</v>
+        <v>560829</v>
       </c>
       <c r="R29" t="n">
-        <v>7309435</v>
+        <v>7309022</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3653,12 +3665,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2014-09-05</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2014-09-05</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3667,39 +3679,38 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>Frodig, urskogsartad granskog i brant terräng</t>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>25090</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Malin Sahlin</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126357748</t>
+          <t>https://artportalen.se/Sighting/66544349</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126358410</v>
+        <v>126357718</v>
       </c>
       <c r="B30" t="n">
-        <v>80433</v>
+        <v>91905</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3707,34 +3718,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Jipmomyran, Jipmomyran, Ly lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>560173</v>
+        <v>560264</v>
       </c>
       <c r="R30" t="n">
-        <v>7309178</v>
+        <v>7309462</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3775,12 +3789,13 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Lövrik grannaturskog</t>
+          <t>Frodig, urskogsartad granskog i brant terräng</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3797,54 +3812,51 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126358410</t>
+          <t>https://artportalen.se/Sighting/126357718</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126358290</v>
+        <v>126359216</v>
       </c>
       <c r="B31" t="n">
-        <v>79327</v>
+        <v>91905</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Jipmomyran, Jipmomyran, Ly lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>560224</v>
+        <v>560542</v>
       </c>
       <c r="R31" t="n">
-        <v>7309210</v>
+        <v>7309328</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3885,13 +3897,12 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Frodig, urskogsartad granskog i brant terräng</t>
+          <t>Lövrik grannaturskog</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -3908,16 +3919,16 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126358290</t>
+          <t>https://artportalen.se/Sighting/126359216</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126357428</v>
+        <v>126358040</v>
       </c>
       <c r="B32" t="n">
-        <v>80432</v>
+        <v>83312</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3925,34 +3936,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>1467</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Järnforsen, Järnforsen, Ly lm</t>
+          <t>Jipmomyran, Jipmomyran, Ly lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>560096</v>
+        <v>560363</v>
       </c>
       <c r="R32" t="n">
-        <v>7309597</v>
+        <v>7309388</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3993,12 +4007,13 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Frodig gråalskog vid bäckdråg</t>
+          <t>Frodig, urskogsartad granskog i brant terräng</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4015,16 +4030,16 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126357428</t>
+          <t>https://artportalen.se/Sighting/126358040</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126358030</v>
+        <v>126357748</v>
       </c>
       <c r="B33" t="n">
-        <v>80432</v>
+        <v>80433</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4032,21 +4047,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4059,10 +4074,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>560363</v>
+        <v>560277</v>
       </c>
       <c r="R33" t="n">
-        <v>7309388</v>
+        <v>7309435</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4126,16 +4141,16 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126358030</t>
+          <t>https://artportalen.se/Sighting/126357748</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126358404</v>
+        <v>126358410</v>
       </c>
       <c r="B34" t="n">
-        <v>80432</v>
+        <v>80433</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4143,21 +4158,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4233,55 +4248,54 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126358404</t>
+          <t>https://artportalen.se/Sighting/126358410</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126357434</v>
+        <v>126358290</v>
       </c>
       <c r="B35" t="n">
-        <v>98186</v>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220250</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Järnforsen, Järnforsen, Ly lm</t>
+          <t>Jipmomyran, Jipmomyran, Ly lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>560096</v>
+        <v>560224</v>
       </c>
       <c r="R35" t="n">
-        <v>7309597</v>
+        <v>7309210</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4328,7 +4342,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>Frodig gråalskog vid bäckdråg</t>
+          <t>Frodig, urskogsartad granskog i brant terräng</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4345,16 +4359,16 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126357434</t>
+          <t>https://artportalen.se/Sighting/126358290</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>66544351</v>
+        <v>126357428</v>
       </c>
       <c r="B36" t="n">
-        <v>92208</v>
+        <v>80432</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4362,37 +4376,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Djupfors V, Ly lm</t>
+          <t>Järnforsen, Järnforsen, Ly lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>560857</v>
+        <v>560096</v>
       </c>
       <c r="R36" t="n">
-        <v>7309015</v>
+        <v>7309597</v>
       </c>
       <c r="S36" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4416,12 +4430,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2014-09-05</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2014-09-05</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4433,35 +4447,35 @@
       <c r="AG36" t="b">
         <v>0</v>
       </c>
-      <c r="AR36" t="inlineStr">
-        <is>
-          <t>25092</t>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>Frodig gråalskog vid bäckdråg</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Malin Sahlin</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66544351</t>
+          <t>https://artportalen.se/Sighting/126357428</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126360392</v>
+        <v>126358030</v>
       </c>
       <c r="B37" t="n">
-        <v>92208</v>
+        <v>80432</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4469,21 +4483,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4496,10 +4510,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>560870</v>
+        <v>560363</v>
       </c>
       <c r="R37" t="n">
-        <v>7309007</v>
+        <v>7309388</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4546,7 +4560,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Grannaturskog/gransumpskog</t>
+          <t>Frodig, urskogsartad granskog i brant terräng</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4563,16 +4577,16 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126360392</t>
+          <t>https://artportalen.se/Sighting/126358030</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>66544348</v>
+        <v>126358404</v>
       </c>
       <c r="B38" t="n">
-        <v>91905</v>
+        <v>80432</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4580,37 +4594,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Djupfors V, Ly lm</t>
+          <t>Jipmomyran, Jipmomyran, Ly lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>560863</v>
+        <v>560173</v>
       </c>
       <c r="R38" t="n">
-        <v>7308993</v>
+        <v>7309178</v>
       </c>
       <c r="S38" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4634,12 +4648,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2014-09-05</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2014-09-05</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4651,73 +4665,74 @@
       <c r="AG38" t="b">
         <v>0</v>
       </c>
-      <c r="AR38" t="inlineStr">
-        <is>
-          <t>25089</t>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>Lövrik grannaturskog</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Malin Sahlin</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66544348</t>
+          <t>https://artportalen.se/Sighting/126358404</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126360330</v>
+        <v>126357434</v>
       </c>
       <c r="B39" t="n">
-        <v>91905</v>
+        <v>98186</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1108</v>
+        <v>220250</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Matteuccia struthiopteris</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Tod.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Jipmomyran, Jipmomyran, Ly lm</t>
+          <t>Järnforsen, Järnforsen, Ly lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>560893</v>
+        <v>560096</v>
       </c>
       <c r="R39" t="n">
-        <v>7308996</v>
+        <v>7309597</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4764,7 +4779,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>Grannaturskog/gransumpskog</t>
+          <t>Frodig gråalskog vid bäckdråg</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -4781,16 +4796,16 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126360330</t>
+          <t>https://artportalen.se/Sighting/126357434</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126360636</v>
+        <v>66544351</v>
       </c>
       <c r="B40" t="n">
-        <v>91905</v>
+        <v>92208</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4798,40 +4813,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1108</v>
+        <v>658</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Jipmomyran, Jipmomyran, Ly lm</t>
+          <t>Djupfors V, Ly lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>560870</v>
+        <v>560857</v>
       </c>
       <c r="R40" t="n">
-        <v>7309007</v>
+        <v>7309015</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4855,12 +4867,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2014-09-05</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2014-09-05</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4869,39 +4881,38 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>Grannaturskog/gransumpskog</t>
+      <c r="AR40" t="inlineStr">
+        <is>
+          <t>25092</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Malin Sahlin</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126360636</t>
+          <t>https://artportalen.se/Sighting/66544351</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>66544343</v>
+        <v>126360392</v>
       </c>
       <c r="B41" t="n">
-        <v>91909</v>
+        <v>92208</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4909,37 +4920,40 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Djupfors V, Ly lm</t>
+          <t>Jipmomyran, Jipmomyran, Ly lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>560934</v>
+        <v>560870</v>
       </c>
       <c r="R41" t="n">
-        <v>7308947</v>
+        <v>7309007</v>
       </c>
       <c r="S41" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4963,12 +4977,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2014-09-05</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2014-09-05</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4977,38 +4991,39 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
-      <c r="AR41" t="inlineStr">
-        <is>
-          <t>25084</t>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>Grannaturskog/gransumpskog</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Malin Sahlin</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66544343</t>
+          <t>https://artportalen.se/Sighting/126360392</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>66544345</v>
+        <v>66544348</v>
       </c>
       <c r="B42" t="n">
-        <v>91909</v>
+        <v>91905</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5016,21 +5031,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5040,10 +5055,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>560922</v>
+        <v>560863</v>
       </c>
       <c r="R42" t="n">
-        <v>7308957</v>
+        <v>7308993</v>
       </c>
       <c r="S42" t="n">
         <v>50</v>
@@ -5089,7 +5104,7 @@
       </c>
       <c r="AR42" t="inlineStr">
         <is>
-          <t>25086</t>
+          <t>25089</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5106,16 +5121,16 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66544345</t>
+          <t>https://artportalen.se/Sighting/66544348</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>66544347</v>
+        <v>126360330</v>
       </c>
       <c r="B43" t="n">
-        <v>91909</v>
+        <v>91905</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5123,37 +5138,40 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Djupfors V, Ly lm</t>
+          <t>Jipmomyran, Jipmomyran, Ly lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>560879</v>
+        <v>560893</v>
       </c>
       <c r="R43" t="n">
-        <v>7308993</v>
+        <v>7308996</v>
       </c>
       <c r="S43" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5177,12 +5195,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2014-09-05</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2014-09-05</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5191,38 +5209,39 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
-      <c r="AR43" t="inlineStr">
-        <is>
-          <t>25088</t>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>Grannaturskog/gransumpskog</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Malin Sahlin</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66544347</t>
+          <t>https://artportalen.se/Sighting/126360330</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>66544350</v>
+        <v>126360636</v>
       </c>
       <c r="B44" t="n">
-        <v>91909</v>
+        <v>91905</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5230,37 +5249,40 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Djupfors V, Ly lm</t>
+          <t>Jipmomyran, Jipmomyran, Ly lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>560857</v>
+        <v>560870</v>
       </c>
       <c r="R44" t="n">
-        <v>7309015</v>
+        <v>7309007</v>
       </c>
       <c r="S44" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5284,12 +5306,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2014-09-05</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2014-09-05</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5298,35 +5320,36 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
-      <c r="AR44" t="inlineStr">
-        <is>
-          <t>25091</t>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>Grannaturskog/gransumpskog</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Malin Sahlin</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66544350</t>
+          <t>https://artportalen.se/Sighting/126360636</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126360324</v>
+        <v>66544343</v>
       </c>
       <c r="B45" t="n">
         <v>91909</v>
@@ -5355,22 +5378,19 @@
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Jipmomyran, Jipmomyran, Ly lm</t>
+          <t>Djupfors V, Ly lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>560893</v>
+        <v>560934</v>
       </c>
       <c r="R45" t="n">
-        <v>7308996</v>
+        <v>7308947</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5394,12 +5414,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2014-09-05</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2014-09-05</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5408,39 +5428,38 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
-      <c r="AI45" t="inlineStr">
-        <is>
-          <t>Grannaturskog/gransumpskog</t>
+      <c r="AR45" t="inlineStr">
+        <is>
+          <t>25084</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Malin Sahlin</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126360324</t>
+          <t>https://artportalen.se/Sighting/66544343</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126360389</v>
+        <v>66544345</v>
       </c>
       <c r="B46" t="n">
-        <v>92369</v>
+        <v>91909</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5448,40 +5467,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Jipmomyran, Jipmomyran, Ly lm</t>
+          <t>Djupfors V, Ly lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>560870</v>
+        <v>560922</v>
       </c>
       <c r="R46" t="n">
-        <v>7309007</v>
+        <v>7308957</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5505,12 +5521,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2014-09-05</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2014-09-05</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5519,61 +5535,60 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
-      <c r="AI46" t="inlineStr">
-        <is>
-          <t>Grannaturskog/gransumpskog</t>
+      <c r="AR46" t="inlineStr">
+        <is>
+          <t>25086</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Malin Sahlin</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126360389</t>
+          <t>https://artportalen.se/Sighting/66544345</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>66544344</v>
+        <v>66544347</v>
       </c>
       <c r="B47" t="n">
-        <v>92333</v>
+        <v>91909</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4217</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5583,10 +5598,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>560934</v>
+        <v>560879</v>
       </c>
       <c r="R47" t="n">
-        <v>7308947</v>
+        <v>7308993</v>
       </c>
       <c r="S47" t="n">
         <v>50</v>
@@ -5632,7 +5647,7 @@
       </c>
       <c r="AR47" t="inlineStr">
         <is>
-          <t>25085</t>
+          <t>25088</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -5649,38 +5664,38 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66544344</t>
+          <t>https://artportalen.se/Sighting/66544347</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>66544353</v>
+        <v>66544350</v>
       </c>
       <c r="B48" t="n">
-        <v>91872</v>
+        <v>91909</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5739,7 +5754,7 @@
       </c>
       <c r="AR48" t="inlineStr">
         <is>
-          <t>25093</t>
+          <t>25091</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -5756,54 +5771,57 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66544353</t>
+          <t>https://artportalen.se/Sighting/66544350</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>66544346</v>
+        <v>126360324</v>
       </c>
       <c r="B49" t="n">
-        <v>79327</v>
+        <v>91909</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Djupfors V, Ly lm</t>
+          <t>Jipmomyran, Jipmomyran, Ly lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>560922</v>
+        <v>560893</v>
       </c>
       <c r="R49" t="n">
-        <v>7308957</v>
+        <v>7308996</v>
       </c>
       <c r="S49" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5827,12 +5845,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2014-09-05</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2014-09-05</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5841,76 +5859,80 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
-      <c r="AR49" t="inlineStr">
-        <is>
-          <t>25087</t>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>Grannaturskog/gransumpskog</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Malin Sahlin</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66544346</t>
+          <t>https://artportalen.se/Sighting/126360324</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>66544342</v>
+        <v>126360389</v>
       </c>
       <c r="B50" t="n">
-        <v>92632</v>
+        <v>92369</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3298</v>
+        <v>1209</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Djupfors V, Ly lm</t>
+          <t>Jipmomyran, Jipmomyran, Ly lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>560960</v>
+        <v>560870</v>
       </c>
       <c r="R50" t="n">
-        <v>7308918</v>
+        <v>7309007</v>
       </c>
       <c r="S50" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5934,12 +5956,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2014-09-05</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2014-09-05</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5948,76 +5970,77 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
-      <c r="AR50" t="inlineStr">
-        <is>
-          <t>25083</t>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>Grannaturskog/gransumpskog</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Malin Sahlin</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66544342</t>
+          <t>https://artportalen.se/Sighting/126360389</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126361127</v>
+        <v>66544344</v>
       </c>
       <c r="B51" t="n">
-        <v>83298</v>
+        <v>92333</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>492</v>
+        <v>4217</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Djupselet, Djupselet, Ly lm</t>
+          <t>Djupfors V, Ly lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>561403</v>
+        <v>560934</v>
       </c>
       <c r="R51" t="n">
-        <v>7308978</v>
+        <v>7308947</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6041,12 +6064,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2014-09-05</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2014-09-05</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6058,57 +6081,57 @@
       <c r="AG51" t="b">
         <v>0</v>
       </c>
-      <c r="AI51" t="inlineStr">
-        <is>
-          <t>Bördig, grovvuxen grannaturskog</t>
+      <c r="AR51" t="inlineStr">
+        <is>
+          <t>25085</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Malin Sahlin</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126361127</t>
+          <t>https://artportalen.se/Sighting/66544344</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>66544648</v>
+        <v>66544353</v>
       </c>
       <c r="B52" t="n">
-        <v>89292</v>
+        <v>91872</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>510</v>
+        <v>5447</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6118,10 +6141,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>561140</v>
+        <v>560857</v>
       </c>
       <c r="R52" t="n">
-        <v>7308737</v>
+        <v>7309015</v>
       </c>
       <c r="S52" t="n">
         <v>50</v>
@@ -6167,7 +6190,7 @@
       </c>
       <c r="AR52" t="inlineStr">
         <is>
-          <t>25371</t>
+          <t>25093</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6178,61 +6201,57 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Via Malin Sahlin</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66544648</t>
+          <t>https://artportalen.se/Sighting/66544353</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>66544623</v>
+        <v>66544346</v>
       </c>
       <c r="B53" t="n">
-        <v>92208</v>
+        <v>79327</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Djupfors V, Ly lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>561045</v>
+        <v>560922</v>
       </c>
       <c r="R53" t="n">
-        <v>7308850</v>
+        <v>7308957</v>
       </c>
       <c r="S53" t="n">
         <v>50</v>
@@ -6278,7 +6297,7 @@
       </c>
       <c r="AR53" t="inlineStr">
         <is>
-          <t>25347</t>
+          <t>25087</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6289,44 +6308,44 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Via Malin Sahlin</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66544623</t>
+          <t>https://artportalen.se/Sighting/66544346</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>66544638</v>
+        <v>66544342</v>
       </c>
       <c r="B54" t="n">
-        <v>92208</v>
+        <v>92632</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>658</v>
+        <v>3298</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6336,10 +6355,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>561100</v>
+        <v>560960</v>
       </c>
       <c r="R54" t="n">
-        <v>7308822</v>
+        <v>7308918</v>
       </c>
       <c r="S54" t="n">
         <v>50</v>
@@ -6385,7 +6404,7 @@
       </c>
       <c r="AR54" t="inlineStr">
         <is>
-          <t>25361</t>
+          <t>25083</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6396,60 +6415,60 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Via Malin Sahlin</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66544638</t>
+          <t>https://artportalen.se/Sighting/66544342</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>66544645</v>
+        <v>126361127</v>
       </c>
       <c r="B55" t="n">
-        <v>92208</v>
+        <v>83298</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>658</v>
+        <v>492</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Djupfors V, Ly lm</t>
+          <t>Djupselet, Djupselet, Ly lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>561119</v>
+        <v>561403</v>
       </c>
       <c r="R55" t="n">
-        <v>7308748</v>
+        <v>7308978</v>
       </c>
       <c r="S55" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6473,12 +6492,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2014-09-05</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2014-09-05</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6490,35 +6509,35 @@
       <c r="AG55" t="b">
         <v>0</v>
       </c>
-      <c r="AR55" t="inlineStr">
-        <is>
-          <t>25368</t>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>Bördig, grovvuxen grannaturskog</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Malin Sahlin</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Via Malin Sahlin</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66544645</t>
+          <t>https://artportalen.se/Sighting/126361127</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>66544651</v>
+        <v>66544648</v>
       </c>
       <c r="B56" t="n">
-        <v>92208</v>
+        <v>89292</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6526,21 +6545,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>658</v>
+        <v>510</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6599,7 +6618,7 @@
       </c>
       <c r="AR56" t="inlineStr">
         <is>
-          <t>25373</t>
+          <t>25371</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -6616,51 +6635,55 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66544651</t>
+          <t>https://artportalen.se/Sighting/66544648</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>66544633</v>
+        <v>66544623</v>
       </c>
       <c r="B57" t="n">
-        <v>92721</v>
+        <v>92208</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>918</v>
+        <v>658</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Djupfors V, Ly lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>561072</v>
+        <v>561045</v>
       </c>
       <c r="R57" t="n">
-        <v>7308827</v>
+        <v>7308850</v>
       </c>
       <c r="S57" t="n">
         <v>50</v>
@@ -6706,7 +6729,7 @@
       </c>
       <c r="AR57" t="inlineStr">
         <is>
-          <t>25356</t>
+          <t>25347</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -6723,16 +6746,16 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66544633</t>
+          <t>https://artportalen.se/Sighting/66544623</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>66544628</v>
+        <v>66544638</v>
       </c>
       <c r="B58" t="n">
-        <v>91905</v>
+        <v>92208</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6740,21 +6763,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1108</v>
+        <v>658</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6764,10 +6787,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>561045</v>
+        <v>561100</v>
       </c>
       <c r="R58" t="n">
-        <v>7308850</v>
+        <v>7308822</v>
       </c>
       <c r="S58" t="n">
         <v>50</v>
@@ -6813,7 +6836,7 @@
       </c>
       <c r="AR58" t="inlineStr">
         <is>
-          <t>25351</t>
+          <t>25361</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -6830,16 +6853,16 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66544628</t>
+          <t>https://artportalen.se/Sighting/66544638</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>66544630</v>
+        <v>66544645</v>
       </c>
       <c r="B59" t="n">
-        <v>91905</v>
+        <v>92208</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6847,21 +6870,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1108</v>
+        <v>658</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6871,10 +6894,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>561062</v>
+        <v>561119</v>
       </c>
       <c r="R59" t="n">
-        <v>7308843</v>
+        <v>7308748</v>
       </c>
       <c r="S59" t="n">
         <v>50</v>
@@ -6920,7 +6943,7 @@
       </c>
       <c r="AR59" t="inlineStr">
         <is>
-          <t>25353</t>
+          <t>25368</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -6937,16 +6960,16 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66544630</t>
+          <t>https://artportalen.se/Sighting/66544645</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>66544627</v>
+        <v>66544651</v>
       </c>
       <c r="B60" t="n">
-        <v>91909</v>
+        <v>92208</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6954,21 +6977,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6978,10 +7001,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>561045</v>
+        <v>561140</v>
       </c>
       <c r="R60" t="n">
-        <v>7308850</v>
+        <v>7308737</v>
       </c>
       <c r="S60" t="n">
         <v>50</v>
@@ -7027,7 +7050,7 @@
       </c>
       <c r="AR60" t="inlineStr">
         <is>
-          <t>25350</t>
+          <t>25373</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7044,38 +7067,38 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66544627</t>
+          <t>https://artportalen.se/Sighting/66544651</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>66544640</v>
+        <v>66544633</v>
       </c>
       <c r="B61" t="n">
-        <v>91909</v>
+        <v>92721</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>918</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7085,10 +7108,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>561100</v>
+        <v>561072</v>
       </c>
       <c r="R61" t="n">
-        <v>7308822</v>
+        <v>7308827</v>
       </c>
       <c r="S61" t="n">
         <v>50</v>
@@ -7134,7 +7157,7 @@
       </c>
       <c r="AR61" t="inlineStr">
         <is>
-          <t>25363</t>
+          <t>25356</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7151,16 +7174,16 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66544640</t>
+          <t>https://artportalen.se/Sighting/66544633</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>66544646</v>
+        <v>66544628</v>
       </c>
       <c r="B62" t="n">
-        <v>91909</v>
+        <v>91905</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7168,21 +7191,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7192,10 +7215,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>561119</v>
+        <v>561045</v>
       </c>
       <c r="R62" t="n">
-        <v>7308748</v>
+        <v>7308850</v>
       </c>
       <c r="S62" t="n">
         <v>50</v>
@@ -7241,7 +7264,7 @@
       </c>
       <c r="AR62" t="inlineStr">
         <is>
-          <t>25369</t>
+          <t>25351</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -7258,38 +7281,38 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66544646</t>
+          <t>https://artportalen.se/Sighting/66544628</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>66544629</v>
+        <v>66544630</v>
       </c>
       <c r="B63" t="n">
-        <v>91923</v>
+        <v>91905</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1204</v>
+        <v>1108</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7348,7 +7371,7 @@
       </c>
       <c r="AR63" t="inlineStr">
         <is>
-          <t>25352</t>
+          <t>25353</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -7365,54 +7388,54 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66544629</t>
+          <t>https://artportalen.se/Sighting/66544630</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126361165</v>
+        <v>66544627</v>
       </c>
       <c r="B64" t="n">
-        <v>91923</v>
+        <v>91909</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Djupselet, Djupselet, Ly lm</t>
+          <t>Djupfors V, Ly lm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>561436</v>
+        <v>561045</v>
       </c>
       <c r="R64" t="n">
-        <v>7308968</v>
+        <v>7308850</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7436,12 +7459,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2014-09-05</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2014-09-05</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7453,35 +7476,35 @@
       <c r="AG64" t="b">
         <v>0</v>
       </c>
-      <c r="AI64" t="inlineStr">
-        <is>
-          <t>Bördig, grovvuxen grannaturskog</t>
+      <c r="AR64" t="inlineStr">
+        <is>
+          <t>25350</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Malin Sahlin</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Via Malin Sahlin</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126361165</t>
+          <t>https://artportalen.se/Sighting/66544627</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>66544641</v>
+        <v>66544640</v>
       </c>
       <c r="B65" t="n">
-        <v>92369</v>
+        <v>91909</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7489,21 +7512,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7562,7 +7585,7 @@
       </c>
       <c r="AR65" t="inlineStr">
         <is>
-          <t>25364</t>
+          <t>25363</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -7579,16 +7602,16 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66544641</t>
+          <t>https://artportalen.se/Sighting/66544640</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>66544619</v>
+        <v>66544646</v>
       </c>
       <c r="B66" t="n">
-        <v>83173</v>
+        <v>91909</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7596,21 +7619,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7620,10 +7643,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>561027</v>
+        <v>561119</v>
       </c>
       <c r="R66" t="n">
-        <v>7308857</v>
+        <v>7308748</v>
       </c>
       <c r="S66" t="n">
         <v>50</v>
@@ -7669,7 +7692,7 @@
       </c>
       <c r="AR66" t="inlineStr">
         <is>
-          <t>25343</t>
+          <t>25369</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -7686,38 +7709,38 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66544619</t>
+          <t>https://artportalen.se/Sighting/66544646</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>66544632</v>
+        <v>66544629</v>
       </c>
       <c r="B67" t="n">
-        <v>83173</v>
+        <v>91923</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7776,7 +7799,7 @@
       </c>
       <c r="AR67" t="inlineStr">
         <is>
-          <t>25355</t>
+          <t>25352</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -7793,54 +7816,54 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66544632</t>
+          <t>https://artportalen.se/Sighting/66544629</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>66544636</v>
+        <v>126361165</v>
       </c>
       <c r="B68" t="n">
-        <v>83173</v>
+        <v>91923</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Djupfors V, Ly lm</t>
+          <t>Djupselet, Djupselet, Ly lm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>561072</v>
+        <v>561436</v>
       </c>
       <c r="R68" t="n">
-        <v>7308827</v>
+        <v>7308968</v>
       </c>
       <c r="S68" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7864,12 +7887,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2014-09-05</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2014-09-05</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7881,35 +7904,35 @@
       <c r="AG68" t="b">
         <v>0</v>
       </c>
-      <c r="AR68" t="inlineStr">
-        <is>
-          <t>25359</t>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>Bördig, grovvuxen grannaturskog</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Malin Sahlin</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Via Malin Sahlin</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66544636</t>
+          <t>https://artportalen.se/Sighting/126361165</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>66544644</v>
+        <v>66544641</v>
       </c>
       <c r="B69" t="n">
-        <v>83173</v>
+        <v>92369</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7917,21 +7940,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1312</v>
+        <v>1209</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7941,10 +7964,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>561108</v>
+        <v>561100</v>
       </c>
       <c r="R69" t="n">
-        <v>7308772</v>
+        <v>7308822</v>
       </c>
       <c r="S69" t="n">
         <v>50</v>
@@ -7990,7 +8013,7 @@
       </c>
       <c r="AR69" t="inlineStr">
         <is>
-          <t>25367</t>
+          <t>25364</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8007,13 +8030,13 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66544644</t>
+          <t>https://artportalen.se/Sighting/66544641</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>66544649</v>
+        <v>66544619</v>
       </c>
       <c r="B70" t="n">
         <v>83173</v>
@@ -8048,10 +8071,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>561140</v>
+        <v>561027</v>
       </c>
       <c r="R70" t="n">
-        <v>7308737</v>
+        <v>7308857</v>
       </c>
       <c r="S70" t="n">
         <v>50</v>
@@ -8097,7 +8120,7 @@
       </c>
       <c r="AR70" t="inlineStr">
         <is>
-          <t>25372</t>
+          <t>25343</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -8114,16 +8137,16 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66544649</t>
+          <t>https://artportalen.se/Sighting/66544619</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126361121</v>
+        <v>66544632</v>
       </c>
       <c r="B71" t="n">
-        <v>83312</v>
+        <v>83173</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8131,37 +8154,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1467</v>
+        <v>1312</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Djupselet, Djupselet, Ly lm</t>
+          <t>Djupfors V, Ly lm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>561403</v>
+        <v>561062</v>
       </c>
       <c r="R71" t="n">
-        <v>7308978</v>
+        <v>7308843</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8185,12 +8208,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2014-09-05</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2014-09-05</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8202,57 +8225,57 @@
       <c r="AG71" t="b">
         <v>0</v>
       </c>
-      <c r="AI71" t="inlineStr">
-        <is>
-          <t>Bördig, grovvuxen grannaturskog</t>
+      <c r="AR71" t="inlineStr">
+        <is>
+          <t>25355</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Malin Sahlin</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Via Malin Sahlin</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126361121</t>
+          <t>https://artportalen.se/Sighting/66544632</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>66544634</v>
+        <v>66544636</v>
       </c>
       <c r="B72" t="n">
-        <v>91872</v>
+        <v>83173</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8311,7 +8334,7 @@
       </c>
       <c r="AR72" t="inlineStr">
         <is>
-          <t>25357</t>
+          <t>25359</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -8328,38 +8351,38 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66544634</t>
+          <t>https://artportalen.se/Sighting/66544636</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>66544341</v>
+        <v>66544644</v>
       </c>
       <c r="B73" t="n">
-        <v>79327</v>
+        <v>83173</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8369,10 +8392,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>561009</v>
+        <v>561108</v>
       </c>
       <c r="R73" t="n">
-        <v>7308906</v>
+        <v>7308772</v>
       </c>
       <c r="S73" t="n">
         <v>50</v>
@@ -8418,7 +8441,7 @@
       </c>
       <c r="AR73" t="inlineStr">
         <is>
-          <t>25082</t>
+          <t>25367</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -8429,61 +8452,57 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Via Malin Sahlin</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66544341</t>
+          <t>https://artportalen.se/Sighting/66544644</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>66544622</v>
+        <v>66544649</v>
       </c>
       <c r="B74" t="n">
-        <v>79327</v>
+        <v>83173</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Djupfors V, Ly lm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>561027</v>
+        <v>561140</v>
       </c>
       <c r="R74" t="n">
-        <v>7308857</v>
+        <v>7308737</v>
       </c>
       <c r="S74" t="n">
         <v>50</v>
@@ -8529,7 +8548,7 @@
       </c>
       <c r="AR74" t="inlineStr">
         <is>
-          <t>25346</t>
+          <t>25372</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -8546,58 +8565,54 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66544622</t>
+          <t>https://artportalen.se/Sighting/66544649</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>66544626</v>
+        <v>126361121</v>
       </c>
       <c r="B75" t="n">
-        <v>79327</v>
+        <v>83312</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Djupfors V, Ly lm</t>
+          <t>Djupselet, Djupselet, Ly lm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>561045</v>
+        <v>561403</v>
       </c>
       <c r="R75" t="n">
-        <v>7308850</v>
+        <v>7308978</v>
       </c>
       <c r="S75" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8621,12 +8636,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2014-09-05</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2014-09-05</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8638,74 +8653,70 @@
       <c r="AG75" t="b">
         <v>0</v>
       </c>
-      <c r="AR75" t="inlineStr">
-        <is>
-          <t>25349</t>
+      <c r="AI75" t="inlineStr">
+        <is>
+          <t>Bördig, grovvuxen grannaturskog</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Malin Sahlin</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Via Malin Sahlin</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66544626</t>
+          <t>https://artportalen.se/Sighting/126361121</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>66544631</v>
+        <v>66544634</v>
       </c>
       <c r="B76" t="n">
-        <v>79327</v>
+        <v>91872</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Djupfors V, Ly lm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>561062</v>
+        <v>561072</v>
       </c>
       <c r="R76" t="n">
-        <v>7308843</v>
+        <v>7308827</v>
       </c>
       <c r="S76" t="n">
         <v>50</v>
@@ -8751,7 +8762,7 @@
       </c>
       <c r="AR76" t="inlineStr">
         <is>
-          <t>25354</t>
+          <t>25357</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -8768,13 +8779,13 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66544631</t>
+          <t>https://artportalen.se/Sighting/66544634</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>66544635</v>
+        <v>66544341</v>
       </c>
       <c r="B77" t="n">
         <v>79327</v>
@@ -8802,21 +8813,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Djupfors V, Ly lm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>561072</v>
+        <v>561009</v>
       </c>
       <c r="R77" t="n">
-        <v>7308827</v>
+        <v>7308906</v>
       </c>
       <c r="S77" t="n">
         <v>50</v>
@@ -8862,7 +8869,7 @@
       </c>
       <c r="AR77" t="inlineStr">
         <is>
-          <t>25358</t>
+          <t>25082</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -8873,19 +8880,19 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Via Malin Sahlin</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66544635</t>
+          <t>https://artportalen.se/Sighting/66544341</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>66544639</v>
+        <v>66544622</v>
       </c>
       <c r="B78" t="n">
         <v>79327</v>
@@ -8924,10 +8931,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>561100</v>
+        <v>561027</v>
       </c>
       <c r="R78" t="n">
-        <v>7308822</v>
+        <v>7308857</v>
       </c>
       <c r="S78" t="n">
         <v>50</v>
@@ -8973,7 +8980,7 @@
       </c>
       <c r="AR78" t="inlineStr">
         <is>
-          <t>25362</t>
+          <t>25346</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -8990,13 +8997,13 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66544639</t>
+          <t>https://artportalen.se/Sighting/66544622</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>66544643</v>
+        <v>66544626</v>
       </c>
       <c r="B79" t="n">
         <v>79327</v>
@@ -9035,10 +9042,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>561108</v>
+        <v>561045</v>
       </c>
       <c r="R79" t="n">
-        <v>7308772</v>
+        <v>7308850</v>
       </c>
       <c r="S79" t="n">
         <v>50</v>
@@ -9084,7 +9091,7 @@
       </c>
       <c r="AR79" t="inlineStr">
         <is>
-          <t>25366</t>
+          <t>25349</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -9101,13 +9108,13 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66544643</t>
+          <t>https://artportalen.se/Sighting/66544626</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>66544647</v>
+        <v>66544631</v>
       </c>
       <c r="B80" t="n">
         <v>79327</v>
@@ -9146,10 +9153,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>561119</v>
+        <v>561062</v>
       </c>
       <c r="R80" t="n">
-        <v>7308748</v>
+        <v>7308843</v>
       </c>
       <c r="S80" t="n">
         <v>50</v>
@@ -9195,7 +9202,7 @@
       </c>
       <c r="AR80" t="inlineStr">
         <is>
-          <t>25370</t>
+          <t>25354</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -9212,51 +9219,55 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66544647</t>
+          <t>https://artportalen.se/Sighting/66544631</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>66544621</v>
+        <v>66544635</v>
       </c>
       <c r="B81" t="n">
-        <v>57953</v>
+        <v>79327</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Djupfors V, Ly lm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>561027</v>
+        <v>561072</v>
       </c>
       <c r="R81" t="n">
-        <v>7308857</v>
+        <v>7308827</v>
       </c>
       <c r="S81" t="n">
         <v>50</v>
@@ -9302,7 +9313,7 @@
       </c>
       <c r="AR81" t="inlineStr">
         <is>
-          <t>25345</t>
+          <t>25358</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -9319,51 +9330,55 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66544621</t>
+          <t>https://artportalen.se/Sighting/66544635</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>66544625</v>
+        <v>66544639</v>
       </c>
       <c r="B82" t="n">
-        <v>57953</v>
+        <v>79327</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Djupfors V, Ly lm</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>561045</v>
+        <v>561100</v>
       </c>
       <c r="R82" t="n">
-        <v>7308850</v>
+        <v>7308822</v>
       </c>
       <c r="S82" t="n">
         <v>50</v>
@@ -9409,7 +9424,7 @@
       </c>
       <c r="AR82" t="inlineStr">
         <is>
-          <t>25348</t>
+          <t>25362</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -9426,51 +9441,55 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66544625</t>
+          <t>https://artportalen.se/Sighting/66544639</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>66544653</v>
+        <v>66544643</v>
       </c>
       <c r="B83" t="n">
-        <v>91905</v>
+        <v>79327</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Djupfors V, Ly lm</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>561132</v>
+        <v>561108</v>
       </c>
       <c r="R83" t="n">
-        <v>7308696</v>
+        <v>7308772</v>
       </c>
       <c r="S83" t="n">
         <v>50</v>
@@ -9516,7 +9535,7 @@
       </c>
       <c r="AR83" t="inlineStr">
         <is>
-          <t>25375</t>
+          <t>25366</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -9533,51 +9552,55 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66544653</t>
+          <t>https://artportalen.se/Sighting/66544643</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>66544652</v>
+        <v>66544647</v>
       </c>
       <c r="B84" t="n">
-        <v>83173</v>
+        <v>79327</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Djupfors V, Ly lm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>561132</v>
+        <v>561119</v>
       </c>
       <c r="R84" t="n">
-        <v>7308696</v>
+        <v>7308748</v>
       </c>
       <c r="S84" t="n">
         <v>50</v>
@@ -9623,7 +9646,7 @@
       </c>
       <c r="AR84" t="inlineStr">
         <is>
-          <t>25374</t>
+          <t>25370</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -9639,6 +9662,434 @@
       </c>
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66544647</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>66544621</v>
+      </c>
+      <c r="B85" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Djupfors V, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>561027</v>
+      </c>
+      <c r="R85" t="n">
+        <v>7308857</v>
+      </c>
+      <c r="S85" t="n">
+        <v>50</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2014-09-05</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2014-09-05</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR85" t="inlineStr">
+        <is>
+          <t>25345</t>
+        </is>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Malin Sahlin</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Via Malin Sahlin</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66544621</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>66544625</v>
+      </c>
+      <c r="B86" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Djupfors V, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>561045</v>
+      </c>
+      <c r="R86" t="n">
+        <v>7308850</v>
+      </c>
+      <c r="S86" t="n">
+        <v>50</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2014-09-05</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2014-09-05</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR86" t="inlineStr">
+        <is>
+          <t>25348</t>
+        </is>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Malin Sahlin</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Via Malin Sahlin</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66544625</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>66544653</v>
+      </c>
+      <c r="B87" t="n">
+        <v>91905</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Djupfors V, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>561132</v>
+      </c>
+      <c r="R87" t="n">
+        <v>7308696</v>
+      </c>
+      <c r="S87" t="n">
+        <v>50</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2014-09-05</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2014-09-05</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR87" t="inlineStr">
+        <is>
+          <t>25375</t>
+        </is>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Malin Sahlin</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Via Malin Sahlin</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66544653</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>66544652</v>
+      </c>
+      <c r="B88" t="n">
+        <v>83173</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Djupfors V, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>561132</v>
+      </c>
+      <c r="R88" t="n">
+        <v>7308696</v>
+      </c>
+      <c r="S88" t="n">
+        <v>50</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2014-09-05</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2014-09-05</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR88" t="inlineStr">
+        <is>
+          <t>25374</t>
+        </is>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Malin Sahlin</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Via Malin Sahlin</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/66544652</t>
         </is>
@@ -9729,6 +10180,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 8219-2025 artfynd.xlsx
+++ b/artfynd/A 8219-2025 artfynd.xlsx
@@ -999,7 +999,7 @@
         <v>137515730</v>
       </c>
       <c r="B5" t="n">
-        <v>99352</v>
+        <v>99355</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>137515731</v>
       </c>
       <c r="B6" t="n">
-        <v>99352</v>
+        <v>99355</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>137515732</v>
       </c>
       <c r="B7" t="n">
-        <v>99352</v>
+        <v>99355</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         <v>137515733</v>
       </c>
       <c r="B24" t="n">
-        <v>99352</v>
+        <v>99355</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
